--- a/fiji/budget_layer_all_years.xlsx
+++ b/fiji/budget_layer_all_years.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3577,7 +3577,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5407,7 +5407,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6487,7 +6487,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6627,7 +6627,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7377,7 +7377,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7697,7 +7697,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7837,7 +7837,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8237,7 +8237,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8807,7 +8807,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -9317,7 +9317,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -9367,7 +9367,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9837,7 +9837,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10497,7 +10497,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10687,7 +10687,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10967,7 +10967,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -11017,7 +11017,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11207,7 +11207,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11437,7 +11437,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11567,7 +11567,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11647,7 +11647,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11747,7 +11747,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -11797,7 +11797,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -11927,7 +11927,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -11977,7 +11977,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12207,7 +12207,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12297,7 +12297,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12347,7 +12347,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12487,7 +12487,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12537,7 +12537,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -12727,7 +12727,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -12767,7 +12767,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -12817,7 +12817,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -12907,7 +12907,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -13047,7 +13047,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -13187,7 +13187,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13377,7 +13377,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -13517,7 +13517,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -13617,7 +13617,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -13767,7 +13767,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -13817,7 +13817,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13907,7 +13907,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13957,7 +13957,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -14057,7 +14057,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -14197,7 +14197,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -14287,7 +14287,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -14527,7 +14527,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -14617,7 +14617,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -14667,7 +14667,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -14707,7 +14707,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -14807,7 +14807,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -14897,7 +14897,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14947,7 +14947,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -15047,7 +15047,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -15087,7 +15087,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -15137,7 +15137,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -15227,7 +15227,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -15367,7 +15367,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -15467,7 +15467,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -15657,7 +15657,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -15757,7 +15757,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -15897,7 +15897,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -15987,7 +15987,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -16037,7 +16037,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -16087,7 +16087,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -16177,7 +16177,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -16277,7 +16277,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -16317,7 +16317,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -16517,7 +16517,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -16557,7 +16557,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -16607,7 +16607,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -16647,7 +16647,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -16697,7 +16697,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -16747,7 +16747,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -16797,7 +16797,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -16837,7 +16837,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -16927,7 +16927,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -17067,7 +17067,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -17207,7 +17207,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -17257,7 +17257,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -17307,7 +17307,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -17397,7 +17397,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -17527,7 +17527,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -17577,7 +17577,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -17677,7 +17677,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>$000</t>
+          <t>FJD thousand</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">

--- a/fiji/budget_layer_all_years.xlsx
+++ b/fiji/budget_layer_all_years.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J367"/>
+  <dimension ref="A1:M367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,21 @@
           <t>source_file</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>programme_class</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>class_source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>strategy_name_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,6 +525,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -560,6 +577,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -600,6 +627,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +679,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -700,6 +739,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -740,6 +789,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -790,6 +841,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -840,6 +901,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -854,7 +925,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MINISTRY OF COMMUNICATION</t>
+          <t>MINISTRY OF COMMUNICATIONS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -880,6 +951,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>MINISTRY OF COMMUNICATION</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -894,7 +972,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MINISTRY OF COMMUNICATION</t>
+          <t>MINISTRY OF COMMUNICATIONS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -930,6 +1008,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>MINISTRY OF COMMUNICATION</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -944,7 +1037,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MINISTRY OF COMMUNICATION</t>
+          <t>MINISTRY OF COMMUNICATIONS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -980,6 +1073,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>MINISTRY OF COMMUNICATION</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -994,7 +1102,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MINISTRY OF COMMUNICATION</t>
+          <t>MINISTRY OF COMMUNICATIONS</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1030,6 +1138,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>MINISTRY OF COMMUNICATION</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1070,6 +1193,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1120,6 +1245,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1160,6 +1295,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1210,6 +1347,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1260,6 +1407,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1310,6 +1467,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1360,6 +1527,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1400,6 +1577,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1450,6 +1629,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1490,6 +1679,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1540,6 +1731,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1590,6 +1791,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1640,6 +1851,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1680,6 +1901,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1730,6 +1953,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1770,6 +2003,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1820,6 +2055,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1870,6 +2115,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1920,6 +2175,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1970,6 +2235,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2020,6 +2295,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2070,6 +2355,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2120,6 +2415,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2170,6 +2475,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2220,6 +2535,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2260,6 +2585,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2310,6 +2637,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2360,6 +2697,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2410,6 +2757,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2460,6 +2817,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2474,7 +2841,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF HOUSING</t>
+          <t>MINISTRY OF HOUSING AND COMMUNITY DEVELOPMENT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2500,6 +2867,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>DEPARTMENT OF HOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2514,7 +2888,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF HOUSING</t>
+          <t>MINISTRY OF HOUSING AND COMMUNITY DEVELOPMENT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2550,6 +2924,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>DEPARTMENT OF HOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2590,6 +2979,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2640,6 +3031,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2690,6 +3091,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2740,6 +3151,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2780,6 +3201,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2830,6 +3253,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2880,6 +3313,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2894,7 +3337,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OFFICE OF THE ATTORNEY GENERAL</t>
+          <t>OFFICE OF THE ATTORNEY - GENERAL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2920,6 +3363,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>OFFICE OF THE ATTORNEY GENERAL</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2934,7 +3384,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OFFICE OF THE ATTORNEY GENERAL</t>
+          <t>OFFICE OF THE ATTORNEY - GENERAL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2970,6 +3420,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>OFFICE OF THE ATTORNEY GENERAL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2984,7 +3449,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OFFICE OF THE ATTORNEY GENERAL</t>
+          <t>OFFICE OF THE ATTORNEY - GENERAL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3020,6 +3485,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>OFFICE OF THE ATTORNEY GENERAL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3060,6 +3540,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3110,6 +3592,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3160,6 +3652,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3210,6 +3712,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3260,6 +3772,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3310,6 +3832,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3350,6 +3882,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3400,6 +3934,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3450,6 +3994,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3490,6 +4044,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3540,6 +4096,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3590,6 +4156,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3630,6 +4206,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3680,6 +4258,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3730,6 +4318,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3780,6 +4378,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3820,6 +4428,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3870,6 +4480,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3920,6 +4540,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3970,6 +4600,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4020,6 +4660,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4070,6 +4720,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4084,7 +4744,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MINISTRY OF SUGAR</t>
+          <t>MINISTRY OF SUGAR INDUSTRY</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4110,6 +4770,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>MINISTRY OF SUGAR</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4124,7 +4791,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>MINISTRY OF SUGAR</t>
+          <t>MINISTRY OF SUGAR INDUSTRY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4160,6 +4827,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>MINISTRY OF SUGAR</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4200,6 +4882,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4250,6 +4934,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4300,6 +4994,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4314,7 +5018,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
+          <t>MINISTRY OF LOCAL GOVERNMENT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4340,6 +5044,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4354,7 +5065,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
+          <t>MINISTRY OF LOCAL GOVERNMENT</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4390,6 +5101,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4404,7 +5130,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
+          <t>MINISTRY OF LOCAL GOVERNMENT</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4440,6 +5166,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4480,6 +5221,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4530,6 +5273,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4570,6 +5323,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4620,6 +5375,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4670,6 +5435,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4710,6 +5485,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4760,6 +5537,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4810,6 +5597,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4860,6 +5657,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4910,6 +5717,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4950,6 +5767,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5000,6 +5819,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5014,7 +5843,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MINISTRY OF WATERWAYS</t>
+          <t>MINISTRY OF WATERWAYS AND ENVIRONMENT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5040,6 +5869,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>MINISTRY OF WATERWAYS</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5054,7 +5890,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MINISTRY OF WATERWAYS</t>
+          <t>MINISTRY OF WATERWAYS AND ENVIRONMENT</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -5090,6 +5926,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>MINISTRY OF WATERWAYS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5104,7 +5955,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MINISTRY OF WATERWAYS</t>
+          <t>MINISTRY OF WATERWAYS AND ENVIRONMENT</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5140,6 +5991,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>MINISTRY OF WATERWAYS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5154,7 +6020,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MINISTRY OF WATERWAYS</t>
+          <t>MINISTRY OF WATERWAYS AND ENVIRONMENT</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5190,6 +6056,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>MINISTRY OF WATERWAYS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5230,6 +6111,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5280,6 +6163,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5320,6 +6213,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5370,6 +6265,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5420,6 +6325,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5460,6 +6375,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5510,6 +6427,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5550,6 +6477,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5600,6 +6529,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5650,6 +6589,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5700,6 +6649,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5750,6 +6709,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5800,6 +6769,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5850,6 +6829,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5900,6 +6889,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5950,6 +6949,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5990,6 +6999,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6040,6 +7051,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6080,6 +7101,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6130,6 +7153,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6180,6 +7213,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6230,6 +7273,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6270,6 +7323,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6320,6 +7375,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6360,6 +7425,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6410,6 +7477,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6450,6 +7527,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6500,6 +7579,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6550,6 +7639,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2017.xlsx</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6590,6 +7689,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6640,6 +7741,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6680,6 +7791,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6730,6 +7843,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6780,6 +7903,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6820,6 +7953,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6870,6 +8005,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6920,6 +8065,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6960,6 +8115,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7010,6 +8167,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7060,6 +8227,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7110,6 +8287,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7150,6 +8337,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7200,6 +8389,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7240,6 +8439,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7290,6 +8491,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7340,6 +8551,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7390,6 +8611,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7430,6 +8661,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -7480,6 +8713,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -7520,6 +8763,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -7570,6 +8815,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -7620,6 +8875,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -7670,6 +8935,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -7710,6 +8985,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7760,6 +9037,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -7800,6 +9087,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -7850,6 +9139,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -7900,6 +9199,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -7950,6 +9259,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8000,6 +9319,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8050,6 +9379,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8100,6 +9439,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8150,6 +9499,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8200,6 +9559,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8250,6 +9619,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8290,6 +9669,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -8340,6 +9721,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -8390,6 +9781,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -8440,6 +9841,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -8490,6 +9901,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -8530,6 +9951,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -8580,6 +10003,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8630,6 +10063,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -8670,6 +10113,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -8720,6 +10165,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -8770,6 +10225,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -8820,6 +10285,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -8860,6 +10335,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -8910,6 +10387,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -8960,6 +10447,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9000,6 +10497,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9050,6 +10549,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9090,6 +10599,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9140,6 +10651,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9190,6 +10711,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9230,6 +10761,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -9280,6 +10813,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9330,6 +10873,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -9380,6 +10933,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -9430,6 +10993,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -9470,6 +11043,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -9520,6 +11095,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -9570,6 +11155,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -9610,6 +11205,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -9660,6 +11257,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -9710,6 +11317,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -9750,6 +11367,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -9800,6 +11419,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -9850,6 +11479,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -9900,6 +11539,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -9940,6 +11589,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -9990,6 +11641,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10040,6 +11701,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10090,6 +11761,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10140,6 +11821,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10190,6 +11881,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -10230,6 +11931,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -10280,6 +11983,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -10294,7 +12007,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>MINISTRY OF PUBLIC ENTERPRISES</t>
+          <t>MINISTRY OF PUBLIC ENTERPRISE</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -10320,6 +12033,13 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>MINISTRY OF PUBLIC ENTERPRISES</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -10334,7 +12054,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>MINISTRY OF PUBLIC ENTERPRISES</t>
+          <t>MINISTRY OF PUBLIC ENTERPRISE</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -10370,6 +12090,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>MINISTRY OF PUBLIC ENTERPRISES</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -10384,7 +12119,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>MINISTRY OF PUBLIC ENTERPRISES</t>
+          <t>MINISTRY OF PUBLIC ENTERPRISE</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -10420,6 +12155,21 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>MINISTRY OF PUBLIC ENTERPRISES</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -10460,6 +12210,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -10510,6 +12262,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -10560,6 +12322,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -10600,6 +12372,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10650,6 +12424,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -10700,6 +12484,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -10740,6 +12534,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -10790,6 +12586,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -10840,6 +12646,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -10890,6 +12706,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -10940,6 +12766,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -10980,6 +12816,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11030,6 +12868,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11070,6 +12918,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -11120,6 +12970,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -11170,6 +13030,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -11220,6 +13090,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -11260,6 +13140,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -11310,6 +13192,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -11350,6 +13242,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -11400,6 +13294,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -11450,6 +13354,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -11490,6 +13404,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -11540,6 +13456,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -11580,6 +13506,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -11620,6 +13548,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11660,6 +13590,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -11710,6 +13642,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -11760,6 +13702,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11810,6 +13762,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -11850,6 +13812,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -11900,6 +13864,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -11940,6 +13914,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -11990,6 +13966,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -12030,6 +14016,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -12080,6 +14068,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -12130,6 +14128,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2018.xlsx</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -12170,6 +14178,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -12220,6 +14230,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -12270,6 +14290,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -12310,6 +14340,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -12360,6 +14392,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -12410,6 +14452,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -12450,6 +14502,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -12500,6 +14554,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -12550,6 +14614,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -12590,6 +14664,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -12640,6 +14716,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -12690,6 +14776,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12740,6 +14836,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -12780,6 +14886,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -12830,6 +14938,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12870,6 +14988,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -12920,6 +15040,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -12970,6 +15100,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -13020,6 +15160,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -13060,6 +15210,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -13110,6 +15262,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -13150,6 +15312,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -13200,6 +15364,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -13250,6 +15424,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -13300,6 +15484,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -13340,6 +15534,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -13390,6 +15586,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -13430,6 +15636,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -13480,6 +15688,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -13530,6 +15748,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -13580,6 +15808,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -13630,6 +15868,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -13680,6 +15928,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -13730,6 +15988,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -13780,6 +16048,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -13830,6 +16108,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -13880,6 +16168,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -13920,6 +16218,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -13970,6 +16270,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -14020,6 +16330,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -14070,6 +16390,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -14120,6 +16450,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -14160,6 +16500,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -14210,6 +16552,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -14260,6 +16612,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -14300,6 +16662,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -14350,6 +16714,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -14400,6 +16774,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -14450,6 +16834,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -14490,6 +16884,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -14540,6 +16936,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -14590,6 +16996,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -14630,6 +17046,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -14680,6 +17098,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -14720,6 +17148,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -14770,6 +17200,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -14820,6 +17260,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -14860,6 +17310,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -14910,6 +17362,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -14960,6 +17422,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -15010,6 +17482,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -15060,6 +17542,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -15100,6 +17592,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -15150,6 +17644,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -15200,6 +17704,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -15240,6 +17754,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr"/>
+      <c r="L315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -15290,6 +17806,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -15340,6 +17866,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -15380,6 +17916,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -15430,6 +17968,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -15480,6 +18028,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -15530,6 +18088,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -15570,6 +18138,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -15620,6 +18190,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -15670,6 +18250,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -15720,6 +18310,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -15770,6 +18370,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -15820,6 +18430,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -15870,6 +18490,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -15910,6 +18540,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -15960,6 +18592,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -16000,6 +18642,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -16050,6 +18694,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -16100,6 +18754,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -16140,6 +18804,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -16190,6 +18856,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -16240,6 +18916,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -16290,6 +18976,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -16330,6 +19026,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -16380,6 +19078,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -16430,6 +19138,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -16480,6 +19198,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -16530,6 +19258,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -16570,6 +19308,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -16620,6 +19360,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -16660,6 +19410,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr"/>
+      <c r="L345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -16710,6 +19462,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -16760,6 +19522,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -16810,6 +19582,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -16850,6 +19632,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr"/>
+      <c r="L349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -16900,6 +19684,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>development</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -16940,6 +19734,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -16990,6 +19786,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -17040,6 +19846,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -17080,6 +19896,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -17130,6 +19948,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -17170,6 +19998,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -17220,6 +20050,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -17270,6 +20110,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -17320,6 +20170,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -17360,6 +20220,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -17410,6 +20272,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -17450,6 +20322,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -17500,6 +20374,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -17540,6 +20424,8 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -17590,6 +20476,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -17640,6 +20536,16 @@
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>standing_function</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -17688,6 +20594,16 @@
       <c r="J367" t="inlineStr">
         <is>
           <t>/Users/sebastianpasha/Developer/Environment_UNDP/PV2/Files/llm/fiji/fiji_budget_2019.xlsx</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>overhead</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>model</t>
         </is>
       </c>
     </row>

--- a/fiji/budget_layer_all_years.xlsx
+++ b/fiji/budget_layer_all_years.xlsx
@@ -9,8 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="budget_all_years" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="programs_wide" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="national_total" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reconciliation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data_quality" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23582,7 +23583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23593,27 +23594,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>head_total</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>strategy_total</t>
+          <t>programme_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>program_sum</t>
+          <t>gap_pct</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>diff</t>
+          <t>basis</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>nested_heads</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>national</t>
         </is>
       </c>
     </row>
@@ -23623,2806 +23629,79 @@
           <t>2017</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4171380.4</v>
       </c>
       <c r="C2" t="n">
-        <v>2144.6</v>
+        <v>4154697.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2144.6</v>
-      </c>
-      <c r="E2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="G2" t="n">
+        <v>4171380.4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>4529133.6</v>
       </c>
       <c r="C3" t="n">
-        <v>23980</v>
+        <v>3944011</v>
       </c>
       <c r="D3" t="n">
-        <v>23980</v>
-      </c>
-      <c r="E3" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>programmes</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+      <c r="G3" t="n">
+        <v>3944011</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3268563.2</v>
       </c>
       <c r="C4" t="n">
-        <v>22314.5</v>
+        <v>3413014.2</v>
       </c>
       <c r="D4" t="n">
-        <v>22314.5</v>
-      </c>
-      <c r="E4" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>heads</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>117275.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>117275.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>13214.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>13214.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5236.7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>5236.7</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>16487</v>
-      </c>
-      <c r="D8" t="n">
-        <v>16487</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>43885</v>
-      </c>
-      <c r="D9" t="n">
-        <v>43885</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>15178.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>15178.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>46722</v>
-      </c>
-      <c r="D11" t="n">
-        <v>46722</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>55363.6</v>
-      </c>
-      <c r="D12" t="n">
-        <v>55363.6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>69032.60000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>69032.60000000001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>20480.3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>20480.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>96688.5</v>
-      </c>
-      <c r="D15" t="n">
-        <v>96688.5</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>148798.8</v>
-      </c>
-      <c r="D16" t="n">
-        <v>148798.8</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>490115.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>490115.7000000001</v>
-      </c>
-      <c r="E17" t="n">
-        <v>-5.820766091346741e-11</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>321245.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>321245.4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.1999999999534339</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>34637.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>34637.2</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>113354.1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>113354</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.1000000000058208</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>23096.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>23096.7</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-0.09999999999854481</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>86339</v>
-      </c>
-      <c r="D22" t="n">
-        <v>86338.99999999999</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1.455191522836685e-11</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>18809.2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>18809.2</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>16020.9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>16020.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>42329.9</v>
-      </c>
-      <c r="D25" t="n">
-        <v>28538.8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>13791.1</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>108382.8</v>
-      </c>
-      <c r="D26" t="n">
-        <v>108382.8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1.455191522836685e-11</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>60021</v>
-      </c>
-      <c r="D27" t="n">
-        <v>60021</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>17939.8</v>
-      </c>
-      <c r="D28" t="n">
-        <v>17939.8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>33927.8</v>
-      </c>
-      <c r="D29" t="n">
-        <v>33927.8</v>
-      </c>
-      <c r="E29" t="n">
-        <v>7.275957614183426e-12</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>7336.1</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7336.1</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>134178</v>
-      </c>
-      <c r="D31" t="n">
-        <v>133737.9</v>
-      </c>
-      <c r="E31" t="n">
-        <v>440.1000000000058</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>306942.7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>306942.7</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>24200</v>
-      </c>
-      <c r="D33" t="n">
-        <v>24200</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>527548.6</v>
-      </c>
-      <c r="D34" t="n">
-        <v>527548.6</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>79207.7</v>
-      </c>
-      <c r="D35" t="n">
-        <v>79207.7</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>628116.8</v>
-      </c>
-      <c r="D36" t="n">
-        <v>615572.2</v>
-      </c>
-      <c r="E36" t="n">
-        <v>12544.60000000009</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>46221.1</v>
-      </c>
-      <c r="D37" t="n">
-        <v>46221.1</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>354607.9</v>
-      </c>
-      <c r="D38" t="n">
-        <v>364701</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-10093.09999999998</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>3127.2</v>
-      </c>
-      <c r="D39" t="n">
-        <v>3127.2</v>
-      </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>14262.3</v>
-      </c>
-      <c r="D40" t="n">
-        <v>23891.3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-9629</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>13708.4</v>
-      </c>
-      <c r="D41" t="n">
-        <v>17708.4</v>
-      </c>
-      <c r="E41" t="n">
-        <v>-4000.000000000002</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>109562.1</v>
-      </c>
-      <c r="D42" t="n">
-        <v>94269.60000000001</v>
-      </c>
-      <c r="E42" t="n">
-        <v>15292.5</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>15069.1</v>
-      </c>
-      <c r="D43" t="n">
-        <v>14241.8</v>
-      </c>
-      <c r="E43" t="n">
-        <v>827.3000000000011</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>4599</v>
-      </c>
-      <c r="D44" t="n">
-        <v>4599</v>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>15989</v>
-      </c>
-      <c r="D45" t="n">
-        <v>15989</v>
-      </c>
-      <c r="E45" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>46964.9</v>
-      </c>
-      <c r="D46" t="n">
-        <v>46964.9</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>15525.6</v>
-      </c>
-      <c r="D47" t="n">
-        <v>15525.6</v>
-      </c>
-      <c r="E47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>49265</v>
-      </c>
-      <c r="D48" t="n">
-        <v>49265</v>
-      </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>64951.2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>64951.2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>51994.4</v>
-      </c>
-      <c r="D50" t="n">
-        <v>51994.4</v>
-      </c>
-      <c r="E50" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>21678.3</v>
-      </c>
-      <c r="D51" t="n">
-        <v>21678.3</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-3.637978807091713e-12</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>103252.1</v>
-      </c>
-      <c r="D52" t="n">
-        <v>103252.1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>193509.9</v>
-      </c>
-      <c r="D53" t="n">
-        <v>193509.9</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>535365.7</v>
-      </c>
-      <c r="D54" t="n">
-        <v>558619.5999999999</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-23253.89999999991</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>334960.2</v>
-      </c>
-      <c r="D55" t="n">
-        <v>334960.2</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>41422.6</v>
-      </c>
-      <c r="D56" t="n">
-        <v>41422.6</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>132997.2</v>
-      </c>
-      <c r="D57" t="n">
-        <v>132997.2</v>
-      </c>
-      <c r="E57" t="n">
-        <v>2.91038304567337e-11</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>24095.9</v>
-      </c>
-      <c r="D58" t="n">
-        <v>23095.8</v>
-      </c>
-      <c r="E58" t="n">
-        <v>1000.100000000002</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>123789.1</v>
-      </c>
-      <c r="D59" t="n">
-        <v>123789.1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>96837.10000000001</v>
-      </c>
-      <c r="D60" t="n">
-        <v>96837</v>
-      </c>
-      <c r="E60" t="n">
-        <v>0.1000000000058208</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>20533.8</v>
-      </c>
-      <c r="D61" t="n">
-        <v>20533.8</v>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>17065.6</v>
-      </c>
-      <c r="D62" t="n">
-        <v>17065.6</v>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>37487.7</v>
-      </c>
-      <c r="D63" t="n">
-        <v>37487.7</v>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>99258.7</v>
-      </c>
-      <c r="D64" t="n">
-        <v>99258.89999999999</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-0.1999999999970896</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>62331.9</v>
-      </c>
-      <c r="D65" t="n">
-        <v>62331.9</v>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>15844.4</v>
-      </c>
-      <c r="D66" t="n">
-        <v>15844.4</v>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>30126.1</v>
-      </c>
-      <c r="D67" t="n">
-        <v>30126</v>
-      </c>
-      <c r="E67" t="n">
-        <v>0.09999999999854481</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>165226.9</v>
-      </c>
-      <c r="D68" t="n">
-        <v>165226.4</v>
-      </c>
-      <c r="E68" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>349264.2</v>
-      </c>
-      <c r="D69" t="n">
-        <v>349264.2</v>
-      </c>
-      <c r="E69" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>69955.7</v>
-      </c>
-      <c r="D70" t="n">
-        <v>69955.70000000001</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-1.455191522836685e-11</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>563056.9</v>
-      </c>
-      <c r="D71" t="n">
-        <v>563056.9</v>
-      </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>80696</v>
-      </c>
-      <c r="D72" t="n">
-        <v>80696</v>
-      </c>
-      <c r="E72" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>567864</v>
-      </c>
-      <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="n">
-        <v>567864</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>46221.1</v>
-      </c>
-      <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="n">
-        <v>46221.1</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>391274.3</v>
-      </c>
-      <c r="D75" t="n">
-        <v>400474.3</v>
-      </c>
-      <c r="E75" t="n">
-        <v>-9200.000000000058</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>3064.2</v>
-      </c>
-      <c r="D76" t="n">
-        <v>3064.2</v>
-      </c>
-      <c r="E76" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>17082.7</v>
-      </c>
-      <c r="D77" t="n">
-        <v>17082.7</v>
-      </c>
-      <c r="E77" t="n">
-        <v>0</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>10659.4</v>
-      </c>
-      <c r="D78" t="n">
-        <v>10659.4</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-1.818989403545856e-12</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>86087.8</v>
-      </c>
-      <c r="D79" t="n">
-        <v>86087.8</v>
-      </c>
-      <c r="E79" t="n">
-        <v>0</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>14546.3</v>
-      </c>
-      <c r="D80" t="n">
-        <v>14546.3</v>
-      </c>
-      <c r="E80" t="n">
-        <v>0</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>16181.5</v>
-      </c>
-      <c r="D81" t="n">
-        <v>16181.5</v>
-      </c>
-      <c r="E81" t="n">
-        <v>0</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>13383.6</v>
-      </c>
-      <c r="D82" t="n">
-        <v>13383.6</v>
-      </c>
-      <c r="E82" t="n">
-        <v>0</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>43261</v>
-      </c>
-      <c r="D83" t="n">
-        <v>43261</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>12785.1</v>
-      </c>
-      <c r="D84" t="n">
-        <v>12784.9</v>
-      </c>
-      <c r="E84" t="n">
-        <v>0.1999999999989086</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>41889</v>
-      </c>
-      <c r="D85" t="n">
-        <v>41889</v>
-      </c>
-      <c r="E85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>74611.39999999999</v>
-      </c>
-      <c r="D86" t="n">
-        <v>74611.3</v>
-      </c>
-      <c r="E86" t="n">
-        <v>0.09999999999126885</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>3271.3</v>
-      </c>
-      <c r="D87" t="n">
-        <v>3271.3</v>
-      </c>
-      <c r="E87" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>18692.2</v>
-      </c>
-      <c r="D88" t="n">
-        <v>18692.2</v>
-      </c>
-      <c r="E88" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>95922.89999999999</v>
-      </c>
-      <c r="D89" t="n">
-        <v>95922.89999999999</v>
-      </c>
-      <c r="E89" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>177789.4</v>
-      </c>
-      <c r="D90" t="n">
-        <v>177789.4</v>
-      </c>
-      <c r="E90" t="n">
-        <v>0</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>467653.9</v>
-      </c>
-      <c r="D91" t="n">
-        <v>467653.9</v>
-      </c>
-      <c r="E91" t="n">
-        <v>0</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>349774.2</v>
-      </c>
-      <c r="D92" t="n">
-        <v>349774.1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>0.1000000000349246</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>17176</v>
-      </c>
-      <c r="D93" t="n">
-        <v>17176</v>
-      </c>
-      <c r="E93" t="n">
-        <v>0</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>127684</v>
-      </c>
-      <c r="D94" t="n">
-        <v>127684</v>
-      </c>
-      <c r="E94" t="n">
-        <v>-1.455191522836685e-11</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>19898.7</v>
-      </c>
-      <c r="D95" t="n">
-        <v>19696.7</v>
-      </c>
-      <c r="E95" t="n">
-        <v>202</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>115587.2</v>
-      </c>
-      <c r="D96" t="n">
-        <v>115587.2</v>
-      </c>
-      <c r="E96" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>78715.89999999999</v>
-      </c>
-      <c r="D97" t="n">
-        <v>78715.8</v>
-      </c>
-      <c r="E97" t="n">
-        <v>0.09999999999126885</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>17177.7</v>
-      </c>
-      <c r="D98" t="n">
-        <v>17177.7</v>
-      </c>
-      <c r="E98" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>16522.7</v>
-      </c>
-      <c r="D99" t="n">
-        <v>16522.7</v>
-      </c>
-      <c r="E99" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>29627.9</v>
-      </c>
-      <c r="D100" t="n">
-        <v>29627.9</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>67086.7</v>
-      </c>
-      <c r="D101" t="n">
-        <v>84250.3</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-17163.60000000001</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>70395.39999999999</v>
-      </c>
-      <c r="D102" t="n">
-        <v>70395.39999999999</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>28447.3</v>
-      </c>
-      <c r="D103" t="n">
-        <v>28447.3</v>
-      </c>
-      <c r="E103" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>89627.39999999999</v>
-      </c>
-      <c r="D104" t="n">
-        <v>89627.29999999999</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0.1000000000058208</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>258715.7</v>
-      </c>
-      <c r="D105" t="n">
-        <v>258715.7</v>
-      </c>
-      <c r="E105" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>33928.4</v>
-      </c>
-      <c r="D106" t="n">
-        <v>33928.4</v>
-      </c>
-      <c r="E106" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>419426.6</v>
-      </c>
-      <c r="D107" t="n">
-        <v>419426.6</v>
-      </c>
-      <c r="E107" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>77526.8</v>
-      </c>
-      <c r="D108" t="n">
-        <v>77526.8</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>354362.9</v>
-      </c>
-      <c r="D109" t="n">
-        <v>363562.9</v>
-      </c>
-      <c r="E109" t="n">
-        <v>-9200</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>MISMATCH</t>
-        </is>
+      <c r="G4" t="n">
+        <v>3268563.2</v>
       </c>
     </row>
   </sheetData>
@@ -26436,66 +23715,2916 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>severity</t>
+          <t>fiscal_year</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>type</t>
+          <t>strategy_code</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>fiscal_year</t>
+          <t>strategy_total</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>strategy_code</t>
+          <t>program_sum</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>program_code</t>
+          <t>diff</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>detail</t>
+          <t>status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2144.6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2144.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23980</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23980</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22314.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>22314.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>117275.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>117275.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13214.4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>13214.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>5236.7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5236.7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>16487</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16487</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>43885</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43885</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>15178.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15178.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>46722</v>
+      </c>
+      <c r="D11" t="n">
+        <v>46722</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>55363.6</v>
+      </c>
+      <c r="D12" t="n">
+        <v>55363.6</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>69032.60000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>69032.60000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20480.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>20480.3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>96688.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>96688.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>148798.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>148798.8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>490115.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>490115.7000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-5.820766091346741e-11</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>321245.6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>321245.4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1999999999534339</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>34637.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>34637.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>113354.1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>113354</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1000000000058208</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>23096.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23096.7</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.09999999999854481</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>86339</v>
+      </c>
+      <c r="D22" t="n">
+        <v>86338.99999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.455191522836685e-11</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>18809.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>18809.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>16020.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>16020.9</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>42329.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>28538.8</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13791.1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>108382.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>108382.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.455191522836685e-11</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>60021</v>
+      </c>
+      <c r="D27" t="n">
+        <v>60021</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>17939.8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17939.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>33927.8</v>
+      </c>
+      <c r="D29" t="n">
+        <v>33927.8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>7.275957614183426e-12</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7336.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7336.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>134178</v>
+      </c>
+      <c r="D31" t="n">
+        <v>133737.9</v>
+      </c>
+      <c r="E31" t="n">
+        <v>440.1000000000058</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>306942.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>306942.7</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>24200</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24200</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>527548.6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>527548.6</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>79207.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>79207.7</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>628116.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>615572.2</v>
+      </c>
+      <c r="E36" t="n">
+        <v>12544.60000000009</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>46221.1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>46221.1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>354607.9</v>
+      </c>
+      <c r="D38" t="n">
+        <v>364701</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-10093.09999999998</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>3127.2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3127.2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>14262.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>23891.3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-9629</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>13708.4</v>
+      </c>
+      <c r="D41" t="n">
+        <v>17708.4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-4000.000000000002</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>109562.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>94269.60000000001</v>
+      </c>
+      <c r="E42" t="n">
+        <v>15292.5</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>15069.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>14241.8</v>
+      </c>
+      <c r="E43" t="n">
+        <v>827.3000000000011</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4599</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4599</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>15989</v>
+      </c>
+      <c r="D45" t="n">
+        <v>15989</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>46964.9</v>
+      </c>
+      <c r="D46" t="n">
+        <v>46964.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>15525.6</v>
+      </c>
+      <c r="D47" t="n">
+        <v>15525.6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>49265</v>
+      </c>
+      <c r="D48" t="n">
+        <v>49265</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>64951.2</v>
+      </c>
+      <c r="D49" t="n">
+        <v>64951.2</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>51994.4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>51994.4</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>21678.3</v>
+      </c>
+      <c r="D51" t="n">
+        <v>21678.3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-3.637978807091713e-12</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>103252.1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>103252.1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>193509.9</v>
+      </c>
+      <c r="D53" t="n">
+        <v>193509.9</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>535365.7</v>
+      </c>
+      <c r="D54" t="n">
+        <v>558619.5999999999</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-23253.89999999991</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>334960.2</v>
+      </c>
+      <c r="D55" t="n">
+        <v>334960.2</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>41422.6</v>
+      </c>
+      <c r="D56" t="n">
+        <v>41422.6</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>132997.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>132997.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.91038304567337e-11</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>24095.9</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23095.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1000.100000000002</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>123789.1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>123789.1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>96837.10000000001</v>
+      </c>
+      <c r="D60" t="n">
+        <v>96837</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.1000000000058208</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>20533.8</v>
+      </c>
+      <c r="D61" t="n">
+        <v>20533.8</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>17065.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>17065.6</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>37487.7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>37487.7</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>99258.7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>99258.89999999999</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-0.1999999999970896</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>62331.9</v>
+      </c>
+      <c r="D65" t="n">
+        <v>62331.9</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>15844.4</v>
+      </c>
+      <c r="D66" t="n">
+        <v>15844.4</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>30126.1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>30126</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.09999999999854481</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>165226.9</v>
+      </c>
+      <c r="D68" t="n">
+        <v>165226.4</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>349264.2</v>
+      </c>
+      <c r="D69" t="n">
+        <v>349264.2</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>69955.7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>69955.70000000001</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-1.455191522836685e-11</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>563056.9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>563056.9</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>80696</v>
+      </c>
+      <c r="D72" t="n">
+        <v>80696</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>567864</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>567864</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>46221.1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>46221.1</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>391274.3</v>
+      </c>
+      <c r="D75" t="n">
+        <v>400474.3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-9200.000000000058</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3064.2</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3064.2</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>17082.7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>17082.7</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>10659.4</v>
+      </c>
+      <c r="D78" t="n">
+        <v>10659.4</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-1.818989403545856e-12</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>86087.8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>86087.8</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>14546.3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>14546.3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>16181.5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16181.5</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>13383.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>13383.6</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>43261</v>
+      </c>
+      <c r="D83" t="n">
+        <v>43261</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>12785.1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>12784.9</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.1999999999989086</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>41889</v>
+      </c>
+      <c r="D85" t="n">
+        <v>41889</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>74611.39999999999</v>
+      </c>
+      <c r="D86" t="n">
+        <v>74611.3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.09999999999126885</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>3271.3</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3271.3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>18692.2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>18692.2</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>95922.89999999999</v>
+      </c>
+      <c r="D89" t="n">
+        <v>95922.89999999999</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>177789.4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>177789.4</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>467653.9</v>
+      </c>
+      <c r="D91" t="n">
+        <v>467653.9</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>349774.2</v>
+      </c>
+      <c r="D92" t="n">
+        <v>349774.1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.1000000000349246</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>17176</v>
+      </c>
+      <c r="D93" t="n">
+        <v>17176</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>127684</v>
+      </c>
+      <c r="D94" t="n">
+        <v>127684</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-1.455191522836685e-11</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>19898.7</v>
+      </c>
+      <c r="D95" t="n">
+        <v>19696.7</v>
+      </c>
+      <c r="E95" t="n">
+        <v>202</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>115587.2</v>
+      </c>
+      <c r="D96" t="n">
+        <v>115587.2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>78715.89999999999</v>
+      </c>
+      <c r="D97" t="n">
+        <v>78715.8</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.09999999999126885</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>17177.7</v>
+      </c>
+      <c r="D98" t="n">
+        <v>17177.7</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>16522.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>16522.7</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>29627.9</v>
+      </c>
+      <c r="D100" t="n">
+        <v>29627.9</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>67086.7</v>
+      </c>
+      <c r="D101" t="n">
+        <v>84250.3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-17163.60000000001</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>70395.39999999999</v>
+      </c>
+      <c r="D102" t="n">
+        <v>70395.39999999999</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>28447.3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>28447.3</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>89627.39999999999</v>
+      </c>
+      <c r="D104" t="n">
+        <v>89627.29999999999</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.1000000000058208</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>258715.7</v>
+      </c>
+      <c r="D105" t="n">
+        <v>258715.7</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>33928.4</v>
+      </c>
+      <c r="D106" t="n">
+        <v>33928.4</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>419426.6</v>
+      </c>
+      <c r="D107" t="n">
+        <v>419426.6</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>77526.8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>77526.8</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>354362.9</v>
+      </c>
+      <c r="D109" t="n">
+        <v>363562.9</v>
+      </c>
+      <c r="E109" t="n">
+        <v>-9200</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MISMATCH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>severity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fiscal_year</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>strategy_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>program_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
           <t>HIGH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reconciliation_mismatch</t>
+          <t>national_basis_programmes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>programs sum to 321,245.4 but strategy_total is 321,245.6 (gap 0.2) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>head totals sum to 4,529,133.6 but the programmes beneath them sum to 3,944,011.0 (13% apart), so the national total for this year is taken from the PROGRAMME rows. Every share for FY2018 is computed against 3,944,011.0.</t>
         </is>
       </c>
     </row>
@@ -26517,13 +26646,13 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>programs sum to 113,354.0 but strategy_total is 113,354.1 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 321,245.4 but strategy_total is 321,245.6 (gap 0.2) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26545,13 +26674,13 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>programs sum to 23,096.7 but strategy_total is 23,096.6 (gap -0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 113,354.0 but strategy_total is 113,354.1 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26573,13 +26702,13 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>programs sum to 28,538.8 but strategy_total is 42,329.9 (gap 13,791.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 23,096.7 but strategy_total is 23,096.6 (gap -0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26601,13 +26730,13 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>programs sum to 133,737.9 but strategy_total is 134,178.0 (gap 440.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 28,538.8 but strategy_total is 42,329.9 (gap 13,791.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26629,13 +26758,13 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>programs sum to 615,572.2 but strategy_total is 628,116.8 (gap 12,544.6) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 133,737.9 but strategy_total is 134,178.0 (gap 440.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26657,13 +26786,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>programs sum to 364,701.0 but strategy_total is 354,607.9 (gap -10,093.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 615,572.2 but strategy_total is 628,116.8 (gap 12,544.6) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26680,18 +26809,18 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>programs sum to 23,891.3 but strategy_total is 14,262.3 (gap -9,629.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 364,701.0 but strategy_total is 354,607.9 (gap -10,093.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26713,13 +26842,13 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>programs sum to 558,619.6 but strategy_total is 535,365.7 (gap -23,253.9) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 23,891.3 but strategy_total is 14,262.3 (gap -9,629.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26741,13 +26870,13 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>programs sum to 23,095.8 but strategy_total is 24,095.9 (gap 1,000.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 558,619.6 but strategy_total is 535,365.7 (gap -23,253.9) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26769,13 +26898,13 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>programs sum to 17,708.4 but strategy_total is 13,708.4 (gap -4,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 23,095.8 but strategy_total is 24,095.9 (gap 1,000.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26797,13 +26926,13 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>programs sum to 96,837.0 but strategy_total is 96,837.1 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 17,708.4 but strategy_total is 13,708.4 (gap -4,000.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26825,13 +26954,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>programs sum to 99,258.9 but strategy_total is 99,258.7 (gap -0.2) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 96,837.0 but strategy_total is 96,837.1 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26853,13 +26982,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>programs sum to 30,126.0 but strategy_total is 30,126.1 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 99,258.9 but strategy_total is 99,258.7 (gap -0.2) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26881,13 +27010,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>programs sum to 94,269.6 but strategy_total is 109,562.1 (gap 15,292.5) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 30,126.0 but strategy_total is 30,126.1 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26909,13 +27038,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>programs sum to 165,226.4 but strategy_total is 165,226.9 (gap 0.5) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 94,269.6 but strategy_total is 109,562.1 (gap 15,292.5) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26937,13 +27066,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>programs sum to 14,241.8 but strategy_total is 15,069.1 (gap 827.3) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 165,226.4 but strategy_total is 165,226.9 (gap 0.5) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26965,13 +27094,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 567,864.0 (gap 567,864.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 14,241.8 but strategy_total is 15,069.1 (gap 827.3) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -26993,13 +27122,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>programs sum to 0.0 but strategy_total is 46,221.1 (gap 46,221.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 567,864.0 (gap 567,864.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27021,13 +27150,13 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>programs sum to 400,474.3 but strategy_total is 391,274.3 (gap -9,200.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 0.0 but strategy_total is 46,221.1 (gap 46,221.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27044,18 +27173,18 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>programs sum to 12,784.9 but strategy_total is 12,785.1 (gap 0.2) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 400,474.3 but strategy_total is 391,274.3 (gap -9,200.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27077,13 +27206,13 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>programs sum to 74,611.3 but strategy_total is 74,611.4 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 12,784.9 but strategy_total is 12,785.1 (gap 0.2) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27105,13 +27234,13 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>programs sum to 349,774.1 but strategy_total is 349,774.2 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 74,611.3 but strategy_total is 74,611.4 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27133,13 +27262,13 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>programs sum to 19,696.7 but strategy_total is 19,898.7 (gap 202.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 349,774.1 but strategy_total is 349,774.2 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27161,13 +27290,13 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>programs sum to 78,715.8 but strategy_total is 78,715.9 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 19,696.7 but strategy_total is 19,898.7 (gap 202.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27189,13 +27318,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>programs sum to 84,250.3 but strategy_total is 67,086.7 (gap -17,163.6) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 78,715.8 but strategy_total is 78,715.9 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27217,13 +27346,13 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>programs sum to 89,627.3 but strategy_total is 89,627.4 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 84,250.3 but strategy_total is 67,086.7 (gap -17,163.6) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27245,45 +27374,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>programs sum to 363,562.9 but strategy_total is 354,362.9 (gap -9,200.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
+          <t>programs sum to 89,627.3 but strategy_total is 89,627.4 (gap 0.1) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>program_missing_in_year</t>
+          <t>reconciliation_mismatch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>23.2</t>
-        </is>
-      </c>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>program '23.2' (Housing) exists in ['2018', '2019'] but is absent in ['2017'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>programs sum to 363,562.9 but strategy_total is 354,362.9 (gap -9,200.0) - a program line is likely missing or mis-extracted for this strategy-year.</t>
         </is>
       </c>
     </row>
@@ -27305,17 +27430,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>26.1</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>program '26.1' (Higher Education Institutions) exists in ['2018', '2019'] but is absent in ['2017'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '23.2' (Housing) exists in ['2018', '2019'] but is absent in ['2017'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27332,22 +27457,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2017,2018</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>26.1</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>program '13.1' (Policy and Administration) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '26.1' (Higher Education Institutions) exists in ['2018', '2019'] but is absent in ['2017'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27369,17 +27494,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34.6</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>program '34.6' (Micro, Small and Medium Enterprises Central Coordinating Agency) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '13.1' (Policy and Administration) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27401,17 +27526,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>34.6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>program '4.3' (Public Enterprises) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '34.6' (Micro, Small and Medium Enterprises Central Coordinating Agency) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27433,17 +27558,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>program '9.1' (Policy and Administration) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '4.3' (Public Enterprises) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27460,22 +27585,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2018,2019</t>
+          <t>2017,2018</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>program '18.4' (Rehabilitation and Rural Housing) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '9.1' (Policy and Administration) exists in ['2019'] but is absent in ['2017', '2018'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27497,17 +27622,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>program '30.5' (Land Drainage and Flood Protection) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '18.4' (Rehabilitation and Rural Housing) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27529,17 +27654,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>program '38.1' (Environment) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '30.5' (Land Drainage and Flood Protection) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27561,17 +27686,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>program '50.1' (Standard Expenditure Group 1) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '38.1' (Environment) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27598,12 +27723,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>50.10</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>program '50.10' (Standard Expenditure Group 10) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.1' (Standard Expenditure Group 1) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27630,12 +27755,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>program '50.3' (Standard Expenditure Group 3) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.10' (Standard Expenditure Group 10) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27662,12 +27787,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>program '50.5' (Standard Expenditure Group 5) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.3' (Standard Expenditure Group 3) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27694,12 +27819,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>program '50.6' (Standard Expenditure Group 6) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.5' (Standard Expenditure Group 5) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27726,12 +27851,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>program '50.7' (Standard Expenditure Group 7) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.6' (Standard Expenditure Group 6) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27758,12 +27883,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>program '50.8' (Standard Expenditure Group 8) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.7' (Standard Expenditure Group 7) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27790,12 +27915,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>50.9</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>program '50.9' (Standard Expenditure Group 9) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.8' (Standard Expenditure Group 8) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27817,17 +27942,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>51.11</t>
+          <t>50.9</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>program '51.11' (SEG 11) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '50.9' (Standard Expenditure Group 9) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27844,22 +27969,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2018,2019</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>36.1</t>
+          <t>51.11</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>program '36.1' (Public Enterprises Reform) exists in ['2017', '2018'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '51.11' (SEG 11) exists in ['2017'] but is absent in ['2018', '2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
@@ -27886,76 +28011,76 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>36.1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>program '36.5' (Government Printing) exists in ['2017', '2018'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
+          <t>program '36.1' (Public Enterprises Reform) exists in ['2017', '2018'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>large_yoy_swing</t>
+          <t>program_missing_in_year</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2017-&gt;2018</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>program '42.2' changed +1763% (2,909.5 -&gt; 54,208.3) - verify this is real and not an extraction error.</t>
+          <t>program '36.5' (Government Printing) exists in ['2017', '2018'] but is absent in ['2019'] - check whether it was dropped during extraction or genuinely did not exist that year.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>large_yoy_swing</t>
+          <t>zero_amount_programme</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2018-&gt;2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>34.1</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>program '34.1' changed +846% (1,828.0 -&gt; 17,291.2) - verify this is real and not an extraction error.</t>
+          <t>programme carries no money; a strategy matched only to lines like this reads as funded while receiving nothing</t>
         </is>
       </c>
     </row>
@@ -27972,70 +28097,86 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2018-&gt;2019</t>
+          <t>2017-&gt;2018</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>program '6.1' changed +252% (4,599.0 -&gt; 16,181.5) - verify this is real and not an extraction error.</t>
+          <t>program '42.2' changed +1763% (2,909.5 -&gt; 54,208.3) - verify this is real and not an extraction error.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>large_yoy_swing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+          <t>2018-&gt;2019</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>34.1</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>national budget total = 4,171,380.4</t>
+          <t>program '34.1' changed +846% (1,828.0 -&gt; 17,291.2) - verify this is real and not an extraction error.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INFO</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>national_total</t>
+          <t>large_yoy_swing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
+          <t>2018-&gt;2019</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>national budget total = 4,529,133.6</t>
+          <t>program '6.1' changed +252% (4,599.0 -&gt; 16,181.5) - verify this is real and not an extraction error.</t>
         </is>
       </c>
     </row>
@@ -28052,12 +28193,60 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
+        <is>
+          <t>national budget total = 4,171,380.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>national budget total = 3,944,011.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>national_total</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
         <is>
           <t>national budget total = 3,268,563.2</t>
         </is>

--- a/fiji/budget_layer_all_years.xlsx
+++ b/fiji/budget_layer_all_years.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M367"/>
+  <dimension ref="A1:N367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,6 +486,11 @@
           <t>strategy_name_source</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>countable</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -528,6 +533,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,6 +594,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -630,6 +641,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -690,6 +702,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -750,6 +767,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -792,6 +814,7 @@
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -852,6 +875,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -910,6 +938,11 @@
       <c r="L9" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -959,6 +992,7 @@
           <t>MINISTRY OF COMMUNICATION</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1024,6 +1058,11 @@
           <t>MINISTRY OF COMMUNICATION</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1089,6 +1128,11 @@
           <t>MINISTRY OF COMMUNICATION</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1154,6 +1198,11 @@
           <t>MINISTRY OF COMMUNICATION</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1196,6 +1245,7 @@
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1256,6 +1306,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1298,6 +1353,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1358,6 +1414,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1418,6 +1479,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1478,6 +1544,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1538,6 +1609,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1580,6 +1656,7 @@
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1640,6 +1717,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1682,6 +1764,7 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1742,6 +1825,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1802,6 +1890,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1862,6 +1955,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1904,6 +2002,7 @@
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1964,6 +2063,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2006,6 +2110,7 @@
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2066,6 +2171,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2126,6 +2236,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2186,6 +2301,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2246,6 +2366,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2306,6 +2431,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2366,6 +2496,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2426,6 +2561,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2486,6 +2626,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2546,6 +2691,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2588,6 +2738,7 @@
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2648,6 +2799,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2708,6 +2864,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2768,6 +2929,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2826,6 +2992,11 @@
       <c r="L43" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -2875,6 +3046,7 @@
           <t>DEPARTMENT OF HOUSING</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2940,6 +3112,11 @@
           <t>DEPARTMENT OF HOUSING</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2982,6 +3159,7 @@
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3042,6 +3220,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3102,6 +3285,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3162,6 +3350,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3204,6 +3397,7 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3264,6 +3458,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3322,6 +3521,11 @@
       <c r="L52" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -3371,6 +3575,7 @@
           <t>OFFICE OF THE ATTORNEY GENERAL</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3436,6 +3641,11 @@
           <t>OFFICE OF THE ATTORNEY GENERAL</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3501,6 +3711,11 @@
           <t>OFFICE OF THE ATTORNEY GENERAL</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3543,6 +3758,7 @@
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3603,6 +3819,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3663,6 +3884,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3723,6 +3949,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3783,6 +4014,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3843,6 +4079,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3885,6 +4126,7 @@
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3945,6 +4187,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4005,6 +4252,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4047,6 +4299,7 @@
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4107,6 +4360,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4167,6 +4425,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4209,6 +4472,7 @@
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4269,6 +4533,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4329,6 +4598,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4389,6 +4663,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4431,6 +4710,7 @@
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4491,6 +4771,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4551,6 +4836,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4611,6 +4901,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4671,6 +4966,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4729,6 +5029,11 @@
       <c r="L77" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -4778,6 +5083,7 @@
           <t>MINISTRY OF SUGAR</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4843,6 +5149,11 @@
           <t>MINISTRY OF SUGAR</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4885,6 +5196,7 @@
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4945,6 +5257,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5003,6 +5320,11 @@
       <c r="L82" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -5052,6 +5374,7 @@
           <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5117,6 +5440,11 @@
           <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5182,6 +5510,11 @@
           <t>MINISTRY OF LOCAL GOVERNMENT AND HOUSING</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5224,6 +5557,7 @@
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5284,6 +5618,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5326,6 +5665,7 @@
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5386,6 +5726,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5446,6 +5791,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5488,6 +5838,7 @@
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5548,6 +5899,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5608,6 +5964,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5668,6 +6029,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5728,6 +6094,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5770,6 +6141,7 @@
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5828,6 +6200,11 @@
       <c r="L97" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -5877,6 +6254,7 @@
           <t>MINISTRY OF WATERWAYS</t>
         </is>
       </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5942,6 +6320,11 @@
           <t>MINISTRY OF WATERWAYS</t>
         </is>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6007,6 +6390,11 @@
           <t>MINISTRY OF WATERWAYS</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6072,6 +6460,11 @@
           <t>MINISTRY OF WATERWAYS</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6114,6 +6507,7 @@
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6174,6 +6568,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6216,6 +6615,7 @@
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6276,6 +6676,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6336,6 +6741,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6378,6 +6788,7 @@
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6438,6 +6849,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6480,6 +6896,7 @@
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6540,6 +6957,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6600,6 +7022,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6660,6 +7087,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6720,6 +7152,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6780,6 +7217,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6840,6 +7282,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6900,6 +7347,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6960,6 +7412,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7002,6 +7459,7 @@
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7062,6 +7520,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7104,6 +7567,7 @@
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7164,6 +7628,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7224,6 +7693,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7284,6 +7758,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7326,6 +7805,7 @@
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7386,6 +7866,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7428,6 +7913,7 @@
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7488,6 +7974,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7530,6 +8021,7 @@
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7590,6 +8082,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7650,6 +8147,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7692,6 +8194,7 @@
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7752,6 +8255,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7794,6 +8302,7 @@
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7854,6 +8363,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7914,6 +8428,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7956,6 +8475,7 @@
       </c>
       <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8016,6 +8536,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8076,6 +8601,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8118,6 +8648,7 @@
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8178,6 +8709,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8238,6 +8774,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8298,6 +8839,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8340,6 +8886,7 @@
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8400,6 +8947,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8442,6 +8994,7 @@
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8502,6 +9055,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8562,6 +9120,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8622,6 +9185,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8664,6 +9232,7 @@
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8724,6 +9293,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8766,6 +9340,7 @@
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8826,6 +9401,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8886,6 +9466,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8946,6 +9531,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8988,6 +9578,7 @@
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9048,6 +9639,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9090,6 +9686,7 @@
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9150,6 +9747,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9210,6 +9812,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9270,6 +9877,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9330,6 +9942,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9390,6 +10007,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9450,6 +10072,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9510,6 +10137,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -9570,6 +10202,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -9630,6 +10267,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9672,6 +10314,7 @@
       </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9732,6 +10375,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9792,6 +10440,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9852,6 +10505,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9912,6 +10570,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9954,6 +10617,7 @@
       </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10014,6 +10678,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10074,6 +10743,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10116,6 +10790,7 @@
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10176,6 +10851,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10236,6 +10916,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10296,6 +10981,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10338,6 +11028,7 @@
       </c>
       <c r="K179" t="inlineStr"/>
       <c r="L179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10398,6 +11089,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10458,6 +11154,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -10500,6 +11201,7 @@
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -10560,6 +11262,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10602,6 +11309,7 @@
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10662,6 +11370,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10722,6 +11435,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10764,6 +11482,7 @@
       </c>
       <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10824,6 +11543,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10884,6 +11608,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10944,6 +11673,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11004,6 +11738,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11046,6 +11785,7 @@
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11106,6 +11846,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11166,6 +11911,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11208,6 +11958,7 @@
       </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11268,6 +12019,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11328,6 +12084,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11370,6 +12131,7 @@
       </c>
       <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -11430,6 +12192,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -11490,6 +12257,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11550,6 +12322,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11592,6 +12369,7 @@
       </c>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11652,6 +12430,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11712,6 +12495,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11772,6 +12560,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11832,6 +12625,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11892,6 +12690,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11934,6 +12737,7 @@
       </c>
       <c r="K208" t="inlineStr"/>
       <c r="L208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11992,6 +12796,11 @@
       <c r="L209" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
@@ -12041,6 +12850,7 @@
           <t>MINISTRY OF PUBLIC ENTERPRISES</t>
         </is>
       </c>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12106,6 +12916,11 @@
           <t>MINISTRY OF PUBLIC ENTERPRISES</t>
         </is>
       </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12171,6 +12986,11 @@
           <t>MINISTRY OF PUBLIC ENTERPRISES</t>
         </is>
       </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12213,6 +13033,7 @@
       </c>
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12273,6 +13094,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12333,6 +13159,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -12375,6 +13206,7 @@
       </c>
       <c r="K216" t="inlineStr"/>
       <c r="L216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -12435,6 +13267,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12495,6 +13332,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12537,6 +13379,7 @@
       </c>
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12597,6 +13440,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12657,6 +13505,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12717,6 +13570,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12777,6 +13635,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12819,6 +13682,7 @@
       </c>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12879,6 +13743,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12921,6 +13790,7 @@
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12981,6 +13851,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13041,6 +13916,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13101,6 +13981,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13143,6 +14028,7 @@
       </c>
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13203,6 +14089,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13245,6 +14136,7 @@
       </c>
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -13305,6 +14197,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13365,6 +14262,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13407,6 +14309,7 @@
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13467,6 +14370,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13509,6 +14417,7 @@
       </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13551,6 +14460,7 @@
       </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13593,6 +14503,7 @@
       </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13653,6 +14564,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13713,6 +14629,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13773,6 +14694,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13815,6 +14741,7 @@
       </c>
       <c r="K243" t="inlineStr"/>
       <c r="L243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13875,6 +14802,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13917,6 +14849,7 @@
       </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13977,6 +14910,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14019,6 +14957,7 @@
       </c>
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14079,6 +15018,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14139,6 +15083,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -14181,6 +15130,7 @@
       </c>
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14241,6 +15191,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14301,6 +15256,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14343,6 +15303,7 @@
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14403,6 +15364,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14463,6 +15429,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14505,6 +15476,7 @@
       </c>
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14565,6 +15537,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14625,6 +15602,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14667,6 +15649,7 @@
       </c>
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14727,6 +15710,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14787,6 +15775,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14847,6 +15840,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14889,6 +15887,7 @@
       </c>
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14949,6 +15948,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14991,6 +15995,7 @@
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -15051,6 +16056,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -15111,6 +16121,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15171,6 +16186,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15213,6 +16233,7 @@
       </c>
       <c r="K269" t="inlineStr"/>
       <c r="L269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15273,6 +16294,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15315,6 +16341,7 @@
       </c>
       <c r="K271" t="inlineStr"/>
       <c r="L271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15375,6 +16402,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15435,6 +16467,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15495,6 +16532,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15537,6 +16579,7 @@
       </c>
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15597,6 +16640,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15639,6 +16687,7 @@
       </c>
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15699,6 +16748,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15759,6 +16813,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15819,6 +16878,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15879,6 +16943,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15939,6 +17008,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15999,6 +17073,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -16059,6 +17138,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -16119,6 +17203,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16179,6 +17268,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16221,6 +17315,7 @@
       </c>
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16281,6 +17376,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16341,6 +17441,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16401,6 +17506,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16461,6 +17571,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16503,6 +17618,7 @@
       </c>
       <c r="K292" t="inlineStr"/>
       <c r="L292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16563,6 +17679,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16623,6 +17744,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16665,6 +17791,7 @@
       </c>
       <c r="K295" t="inlineStr"/>
       <c r="L295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16725,6 +17852,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16785,6 +17917,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16845,6 +17982,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16887,6 +18029,7 @@
       </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16947,6 +18090,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -17007,6 +18155,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -17049,6 +18202,7 @@
       </c>
       <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -17109,6 +18263,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -17151,6 +18310,7 @@
       </c>
       <c r="K304" t="inlineStr"/>
       <c r="L304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -17211,6 +18371,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -17271,6 +18436,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17313,6 +18483,7 @@
       </c>
       <c r="K307" t="inlineStr"/>
       <c r="L307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -17373,6 +18544,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17433,6 +18609,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -17493,6 +18674,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -17553,6 +18739,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -17595,6 +18786,7 @@
       </c>
       <c r="K312" t="inlineStr"/>
       <c r="L312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17655,6 +18847,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -17715,6 +18912,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -17757,6 +18959,7 @@
       </c>
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
+      <c r="N315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -17817,6 +19020,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -17877,6 +19085,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17919,6 +19132,7 @@
       </c>
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -17979,6 +19193,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -18039,6 +19258,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -18099,6 +19323,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -18141,6 +19370,7 @@
       </c>
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -18201,6 +19431,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -18261,6 +19496,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18321,6 +19561,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -18381,6 +19626,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18441,6 +19691,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18501,6 +19756,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18543,6 +19803,7 @@
       </c>
       <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -18603,6 +19864,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18645,6 +19911,7 @@
       </c>
       <c r="K331" t="inlineStr"/>
       <c r="L331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -18705,6 +19972,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -18765,6 +20037,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N333" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -18807,6 +20084,7 @@
       </c>
       <c r="K334" t="inlineStr"/>
       <c r="L334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18867,6 +20145,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N335" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -18927,6 +20210,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N336" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -18987,6 +20275,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N337" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -19029,6 +20322,7 @@
       </c>
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -19089,6 +20383,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N339" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -19149,6 +20448,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N340" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -19209,6 +20513,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N341" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -19269,6 +20578,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N342" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -19311,6 +20625,7 @@
       </c>
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -19371,6 +20686,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N344" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -19413,6 +20733,7 @@
       </c>
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
+      <c r="N345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -19473,6 +20794,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N346" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -19533,6 +20859,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N347" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -19593,6 +20924,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N348" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -19635,6 +20971,7 @@
       </c>
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
+      <c r="N349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -19695,6 +21032,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -19737,6 +21079,7 @@
       </c>
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -19797,6 +21140,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -19857,6 +21205,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -19899,6 +21252,7 @@
       </c>
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
+      <c r="N354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -19959,6 +21313,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -20001,6 +21360,7 @@
       </c>
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -20061,6 +21421,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -20121,6 +21486,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -20181,6 +21551,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -20223,6 +21598,7 @@
       </c>
       <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -20283,6 +21659,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -20325,6 +21706,7 @@
       </c>
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -20385,6 +21767,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -20427,6 +21814,7 @@
       </c>
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -20487,6 +21875,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -20547,6 +21940,11 @@
           <t>model</t>
         </is>
       </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -20605,6 +22003,11 @@
       <c r="L367" t="inlineStr">
         <is>
           <t>model</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
     </row>
